--- a/ig/nr-bp-implem/ValueSet-ModifiedAdministrativeGender.xlsx
+++ b/ig/nr-bp-implem/ValueSet-ModifiedAdministrativeGender.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:17:33+00:00</t>
+    <t>2023-05-11T19:33:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-bp-implem/ValueSet-ModifiedAdministrativeGender.xlsx
+++ b/ig/nr-bp-implem/ValueSet-ModifiedAdministrativeGender.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:33:36+00:00</t>
+    <t>2023-05-11T19:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-bp-implem/ValueSet-ModifiedAdministrativeGender.xlsx
+++ b/ig/nr-bp-implem/ValueSet-ModifiedAdministrativeGender.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:47:27+00:00</t>
+    <t>2023-05-12T16:04:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
